--- a/data/attendance/AMPHI_زهراوي_ادبي_1.xlsx
+++ b/data/attendance/AMPHI_زهراوي_ادبي_1.xlsx
@@ -304,7 +304,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
-    <t>زهراوي ادبي 1  |  AMPHI  |  BAC  |  - زهراوي</t>
+    <t>زهراوي ادبي 1  |  AMPHI  |  BAC  |  زهراوي</t>
   </si>
   <si>
     <t>class_id=9</t>

--- a/data/attendance/AMPHI_زهراوي_ادبي_1.xlsx
+++ b/data/attendance/AMPHI_زهراوي_ادبي_1.xlsx
@@ -20,280 +20,329 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <t>student_id:12e80561-aa12-447b-87de-f9fac78f8888</t>
+          <t>student_id:802cad91-388f-435c-8257-1d245c24bc4e</t>
         </r>
       </text>
     </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <t>student_id:6426c12c-9914-4ea0-b7f1-5244eafafb2f</t>
+          <t>student_id:46a6adb3-93c6-412d-aaec-fc96a0919f31</t>
         </r>
       </text>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <t>student_id:f492322c-de39-41e5-a7f1-f9906a8bd5ad</t>
+          <t>student_id:3dcf69d8-4e8e-4743-8254-05fc98dda249</t>
         </r>
       </text>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <t>student_id:cb154650-95ee-4dec-a601-1f898c42fb1d</t>
+          <t>student_id:d133b1c1-28a3-4b97-a9db-6b476ae244b4</t>
         </r>
       </text>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <t>student_id:7bb13f36-1d51-44b0-b90e-8d1d38e59bb8</t>
+          <t>student_id:68c9e7f1-d4ae-4293-b6b9-451268793a45</t>
         </r>
       </text>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <t>student_id:07aa9cd5-b9be-4384-998f-3062fb953d3d</t>
+          <t>student_id:1b525255-15fd-4688-a952-6f984dd055a3</t>
         </r>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <t>student_id:4ba9d769-df8e-4dd1-8987-cb594a9711ff</t>
+          <t>student_id:7e07fd69-a2ce-411a-bd6e-1c0f95d035f2</t>
         </r>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <t>student_id:7445b2d9-5a82-4681-8ab7-84b566490e69</t>
+          <t>student_id:04581ce8-2e3c-4c49-846b-d635898e21a5</t>
         </r>
       </text>
     </comment>
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <t>student_id:6abdfba1-2a20-458a-96cf-f360274b2d25</t>
+          <t>student_id:84ff47b8-ea13-44b3-ab36-236c6f8aab54</t>
         </r>
       </text>
     </comment>
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <t>student_id:51957465-9492-4309-86e0-e9304d718a66</t>
+          <t>student_id:6a75f326-77ad-4d47-9e88-ead02d7c4b58</t>
         </r>
       </text>
     </comment>
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <t>student_id:8ea040d9-f37c-4cba-b1ad-71eee28b9d8c</t>
+          <t>student_id:7978a3d1-f77e-4b38-af22-69725d451de5</t>
         </r>
       </text>
     </comment>
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <t>student_id:18b878bc-3b27-478d-8e90-6f70b0d75882</t>
+          <t>student_id:6306692e-e7ab-4a1f-8f98-a70551e1751c</t>
         </r>
       </text>
     </comment>
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <t>student_id:cb7c2487-edcc-4870-a05e-b15ccdd88360</t>
+          <t>student_id:6d6c578a-c78b-438d-91c0-cf998c2750c3</t>
         </r>
       </text>
     </comment>
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <t>student_id:f6d42770-7103-4b23-96c3-70343dfad899</t>
+          <t>student_id:76c63291-be9c-482f-b4b0-1cabe917d476</t>
         </r>
       </text>
     </comment>
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <t>student_id:2b4ff496-dd65-49bc-b7c8-aa486d49eb32</t>
+          <t>student_id:7d1f60ce-c5d8-4377-91d6-6c4b6023e8f9</t>
         </r>
       </text>
     </comment>
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <t>student_id:f4a2c2b7-e3fc-44e3-b7fd-f6ac2707f5b8</t>
+          <t>student_id:17558c2a-1262-434a-97e3-56eca8a756b1</t>
         </r>
       </text>
     </comment>
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <t>student_id:2244cd7c-cb58-4ee8-bb92-0132e3a83fe5</t>
+          <t>student_id:706ecf15-8a21-4df2-9994-901d88ca9cdc</t>
         </r>
       </text>
     </comment>
     <comment ref="B22" authorId="0">
       <text>
         <r>
-          <t>student_id:54d00d3f-939e-4991-82e1-e4c620ef00ea</t>
+          <t>student_id:d5b643e6-acb1-4b43-b3b1-569248654a73</t>
         </r>
       </text>
     </comment>
     <comment ref="B23" authorId="0">
       <text>
         <r>
-          <t>student_id:8a371c20-e43c-4643-aff9-5ccea0349725</t>
+          <t>student_id:e956e725-6d59-44da-adc3-a8bf8f10dbe4</t>
         </r>
       </text>
     </comment>
     <comment ref="B24" authorId="0">
       <text>
         <r>
-          <t>student_id:b2a08f9a-b6d3-40aa-a473-ec101177bcdd</t>
+          <t>student_id:9a86b640-ceff-4413-93c3-8f7a5733ba8c</t>
         </r>
       </text>
     </comment>
     <comment ref="B25" authorId="0">
       <text>
         <r>
-          <t>student_id:97f81e18-864b-4122-b96c-1d9f9a2108cc</t>
+          <t>student_id:0a7a2f76-33f3-4182-97bd-0e0dff2f6bac</t>
         </r>
       </text>
     </comment>
     <comment ref="B26" authorId="0">
       <text>
         <r>
-          <t>student_id:b85d7dda-bc81-4abe-bcfc-7ce068f52f0d</t>
+          <t>student_id:b99e4fec-b8dd-4831-8de9-5233a20953d7</t>
         </r>
       </text>
     </comment>
     <comment ref="B27" authorId="0">
       <text>
         <r>
-          <t>student_id:7129db68-232b-490a-a466-afe3e23e312f</t>
+          <t>student_id:f884f596-56ad-4371-b485-31a181e29eee</t>
         </r>
       </text>
     </comment>
     <comment ref="B28" authorId="0">
       <text>
         <r>
-          <t>student_id:91ded930-5b10-4bf6-95d8-ed771a0d12ea</t>
+          <t>student_id:4919300a-6f37-4a88-9414-45316707a25f</t>
         </r>
       </text>
     </comment>
     <comment ref="B29" authorId="0">
       <text>
         <r>
-          <t>student_id:2119bc11-d392-4664-8c9c-275b0057b4f0</t>
+          <t>student_id:abbf565a-6277-46a7-9673-f053d01d6e24</t>
         </r>
       </text>
     </comment>
     <comment ref="B30" authorId="0">
       <text>
         <r>
-          <t>student_id:06c280e7-922d-4ab4-a3dd-aebbd06e82b4</t>
+          <t>student_id:0a76d7d3-5f1e-4dc0-bb7d-59b454c144fc</t>
         </r>
       </text>
     </comment>
     <comment ref="B31" authorId="0">
       <text>
         <r>
-          <t>student_id:12c63b78-6810-412b-9305-7c108d22cb2a</t>
+          <t>student_id:794959c2-b85f-46e1-a7e1-9c120b338d9a</t>
         </r>
       </text>
     </comment>
     <comment ref="B32" authorId="0">
       <text>
         <r>
-          <t>student_id:0caa3db3-88ac-4d44-88b2-b36319ea582d</t>
+          <t>student_id:2225a3f3-9a6a-4517-8504-cf7b7da5d5f0</t>
         </r>
       </text>
     </comment>
     <comment ref="B33" authorId="0">
       <text>
         <r>
-          <t>student_id:d9d2b766-ffe5-4b69-a27e-b9d3255d6f80</t>
+          <t>student_id:a2e18186-04fa-473c-9e6c-72d087462166</t>
         </r>
       </text>
     </comment>
     <comment ref="B34" authorId="0">
       <text>
         <r>
-          <t>student_id:b9c2958d-c258-4db7-b768-88fe617196b7</t>
+          <t>student_id:84037c0c-016b-4072-a7bb-3edef521a833</t>
         </r>
       </text>
     </comment>
     <comment ref="B35" authorId="0">
       <text>
         <r>
-          <t>student_id:d7172c89-0a74-42b3-af48-66fe4f5e7d73</t>
+          <t>student_id:6d9c17ac-0f55-4b43-bbb0-b4a1d10a404a</t>
         </r>
       </text>
     </comment>
     <comment ref="B36" authorId="0">
       <text>
         <r>
-          <t>student_id:ce77267c-425e-4ce1-b11c-b7df08994ed8</t>
+          <t>student_id:c2c5e8ca-a7bd-45e8-9793-c7720b5f46fc</t>
         </r>
       </text>
     </comment>
     <comment ref="B37" authorId="0">
       <text>
         <r>
-          <t>student_id:fbb36c23-8313-4775-a454-7a41ba98d316</t>
+          <t>student_id:614f42a5-0e1f-46e7-88d6-c5f7783ee6ec</t>
         </r>
       </text>
     </comment>
     <comment ref="B38" authorId="0">
       <text>
         <r>
-          <t>student_id:ef0ae9cb-f3aa-4d89-909f-3208565f43e4</t>
+          <t>student_id:cf2e9bc3-cc90-454c-8fbe-2a06de627a75</t>
         </r>
       </text>
     </comment>
     <comment ref="B39" authorId="0">
       <text>
         <r>
-          <t>student_id:edbd3f26-9542-4f99-86ee-f5cb75d9fdd1</t>
+          <t>student_id:f0305082-a3a6-46b2-b88c-e76058cb2fc4</t>
         </r>
       </text>
     </comment>
     <comment ref="B40" authorId="0">
       <text>
         <r>
-          <t>student_id:32a31fd2-0963-4522-915b-704155e9b5b3</t>
+          <t>student_id:cd00920f-5475-4e56-90c2-daeadc54ef6d</t>
         </r>
       </text>
     </comment>
     <comment ref="B41" authorId="0">
       <text>
         <r>
-          <t>student_id:73984ba4-8f56-4f2d-b72d-fbad198c18d2</t>
+          <t>student_id:59b4f620-8e75-44c0-aadf-45cabeb9141e</t>
         </r>
       </text>
     </comment>
     <comment ref="B42" authorId="0">
       <text>
         <r>
-          <t>student_id:a789e735-eb9a-4130-86cb-04dc72db34ad</t>
+          <t>student_id:09d38764-9dd3-45fc-ab46-179050340c91</t>
         </r>
       </text>
     </comment>
     <comment ref="B43" authorId="0">
       <text>
         <r>
-          <t>student_id:295fb726-dc78-4501-8452-e1540e587518</t>
+          <t>student_id:940ee804-c513-440b-9492-b6f652d91570</t>
         </r>
       </text>
     </comment>
     <comment ref="B44" authorId="0">
       <text>
         <r>
-          <t>student_id:d1effe36-c9ae-4a43-9822-fd2da68a8fee</t>
+          <t>student_id:5688f6f9-82f1-418f-a5d0-191da4520e6e</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0">
+      <text>
+        <r>
+          <t>student_id:e19083e5-fb52-4474-9b87-f7ac097a6fde</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0">
+      <text>
+        <r>
+          <t>student_id:7e4c10db-0e0f-4122-b9f3-003b7fbc4280</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0">
+      <text>
+        <r>
+          <t>student_id:1ef83844-49f4-4e07-9ba1-3a3d9c7f7fff</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0">
+      <text>
+        <r>
+          <t>student_id:dca6f60c-f366-4dfe-994a-e3534e9ea227</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0">
+      <text>
+        <r>
+          <t>student_id:4915abfb-a955-4ab9-83c8-136c50fe6eae</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0">
+      <text>
+        <r>
+          <t>student_id:1b6a7a9c-c91b-4b10-9e37-4e4fac572776</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0">
+      <text>
+        <r>
+          <t>student_id:09fe61eb-a4f9-4ce6-b563-381fddcf72a0</t>
         </r>
       </text>
     </comment>
@@ -302,7 +351,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>زهراوي ادبي 1  |  AMPHI  |  BAC  |  زهراوي</t>
   </si>
@@ -325,130 +374,151 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
-    <t>05/09/2026</t>
+    <t>26/09/2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>مشري ماريا</t>
+  </si>
+  <si>
+    <t>دلوش ملاك</t>
+  </si>
+  <si>
+    <t>بن لطرش محمد يحي</t>
+  </si>
+  <si>
     <t>مخلوفي ندير</t>
   </si>
   <si>
+    <t>علالة أسماء عبير</t>
+  </si>
+  <si>
+    <t>سطايفي ألاء</t>
+  </si>
+  <si>
+    <t>لموالدي جيهان</t>
+  </si>
+  <si>
+    <t>نجمة هبة الرحمان</t>
+  </si>
+  <si>
+    <t>زواد لجين</t>
+  </si>
+  <si>
+    <t>بيدي وصال أسماء</t>
+  </si>
+  <si>
+    <t>محلول لؤي منيب</t>
+  </si>
+  <si>
+    <t>حوبار تقوى</t>
+  </si>
+  <si>
+    <t>بنونة بهاء</t>
+  </si>
+  <si>
+    <t>قطش فاطمة الزهراء</t>
+  </si>
+  <si>
+    <t>بن جفال منار</t>
+  </si>
+  <si>
     <t>معمري ريتاج</t>
   </si>
   <si>
     <t>مالكي دارين</t>
   </si>
   <si>
+    <t>قندوز ماريا</t>
+  </si>
+  <si>
+    <t>بوصبع احمد ياسين</t>
+  </si>
+  <si>
+    <t>بوحملة رتاج</t>
+  </si>
+  <si>
+    <t>فريفط خديجة</t>
+  </si>
+  <si>
+    <t>بن كرود رتاج</t>
+  </si>
+  <si>
+    <t>بن ساسي هديل</t>
+  </si>
+  <si>
+    <t>كريس امينة</t>
+  </si>
+  <si>
     <t>حطاب ميسون</t>
   </si>
   <si>
-    <t>مشري ماريا</t>
-  </si>
-  <si>
-    <t>بيدي وصال أسماء</t>
+    <t>بودفة عبد الرحيم</t>
+  </si>
+  <si>
+    <t>شماع رتاج</t>
+  </si>
+  <si>
+    <t>قوطاس سيرين</t>
+  </si>
+  <si>
+    <t>شليغم اسراء</t>
+  </si>
+  <si>
+    <t>بولفراخ رنيم</t>
   </si>
   <si>
     <t>سعدوني رنيم</t>
   </si>
   <si>
+    <t>حمودي مريم</t>
+  </si>
+  <si>
+    <t>بلخامسة شيماء</t>
+  </si>
+  <si>
+    <t>صخري اروى</t>
+  </si>
+  <si>
+    <t>شارف غادة</t>
+  </si>
+  <si>
+    <t>نمر حنين</t>
+  </si>
+  <si>
+    <t>ناصر سيرين</t>
+  </si>
+  <si>
+    <t>بن عويرة مقيم</t>
+  </si>
+  <si>
+    <t>مجميع سندس</t>
+  </si>
+  <si>
     <t>سناني ملاك</t>
   </si>
   <si>
-    <t>بن لطرش محمد يحي</t>
-  </si>
-  <si>
-    <t>علالة أسماء عبير</t>
-  </si>
-  <si>
-    <t>سطايفي ألاء</t>
-  </si>
-  <si>
-    <t>لموالدي جيهان</t>
-  </si>
-  <si>
-    <t>نجمة هبة الرحمان</t>
-  </si>
-  <si>
-    <t>زواد لجين</t>
-  </si>
-  <si>
-    <t>محلول لؤي منيب</t>
-  </si>
-  <si>
-    <t>حوبار تقوى</t>
-  </si>
-  <si>
-    <t>بنونة بهاء</t>
-  </si>
-  <si>
-    <t>قطش فاطمة الزهراء</t>
-  </si>
-  <si>
-    <t>بن جفال منار</t>
-  </si>
-  <si>
-    <t>قندوز ماريا</t>
-  </si>
-  <si>
-    <t>بوصبع احمد ياسين</t>
-  </si>
-  <si>
-    <t>بوحملة رتاج</t>
-  </si>
-  <si>
-    <t>فريفط خديجة</t>
-  </si>
-  <si>
-    <t>بن كرود رتاج</t>
-  </si>
-  <si>
-    <t>بن ساسي هديل</t>
-  </si>
-  <si>
-    <t>كريس امينة</t>
-  </si>
-  <si>
-    <t>بودفة عبد الرحيم</t>
-  </si>
-  <si>
-    <t>شماع رتاج</t>
-  </si>
-  <si>
-    <t>قوطاس سيرين</t>
-  </si>
-  <si>
-    <t>شليغم اسراء</t>
-  </si>
-  <si>
-    <t>بولفراخ رنيم</t>
-  </si>
-  <si>
-    <t>حمودي مريم</t>
-  </si>
-  <si>
     <t>داموس محمد</t>
   </si>
   <si>
-    <t>مجمج سندس</t>
-  </si>
-  <si>
-    <t>صخري اروى</t>
-  </si>
-  <si>
-    <t>شارف غادة</t>
-  </si>
-  <si>
-    <t>نمر حنين</t>
-  </si>
-  <si>
     <t>لطرش محمد</t>
   </si>
   <si>
-    <t>بن عويرة مقيم</t>
-  </si>
-  <si>
-    <t>مجميع سندس</t>
+    <t>بغالي ريتاج</t>
+  </si>
+  <si>
+    <t>لوزري انس</t>
+  </si>
+  <si>
+    <t>زيوان احمد</t>
+  </si>
+  <si>
+    <t>عاشور محمد</t>
+  </si>
+  <si>
+    <t>طيار عبد الرحيم</t>
   </si>
   <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
@@ -968,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1093,7 +1163,7 @@
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>47</v>
+        <v>217</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>9</v>
@@ -1137,7 +1207,7 @@
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>49</v>
+        <v>218</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>10</v>
@@ -1181,7 +1251,7 @@
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>11</v>
@@ -1225,7 +1295,7 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>58</v>
+        <v>220</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>12</v>
@@ -1269,7 +1339,7 @@
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>168</v>
+        <v>221</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>13</v>
@@ -1313,7 +1383,7 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>14</v>
@@ -1357,7 +1427,7 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>407</v>
+        <v>223</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>15</v>
@@ -1401,7 +1471,7 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>446</v>
+        <v>224</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>16</v>
@@ -1445,7 +1515,7 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>447</v>
+        <v>225</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1489,7 +1559,7 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>448</v>
+        <v>226</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>18</v>
@@ -1533,7 +1603,7 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>449</v>
+        <v>227</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>19</v>
@@ -1577,7 +1647,7 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>450</v>
+        <v>228</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>20</v>
@@ -1621,7 +1691,7 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>451</v>
+        <v>229</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>21</v>
@@ -1665,7 +1735,7 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>452</v>
+        <v>230</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>22</v>
@@ -1709,7 +1779,7 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>453</v>
+        <v>231</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>23</v>
@@ -1753,7 +1823,7 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>454</v>
+        <v>232</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>24</v>
@@ -1797,7 +1867,7 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>455</v>
+        <v>233</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>25</v>
@@ -1841,7 +1911,7 @@
     </row>
     <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>456</v>
+        <v>234</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>26</v>
@@ -1885,7 +1955,7 @@
     </row>
     <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>457</v>
+        <v>235</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>27</v>
@@ -1929,7 +1999,7 @@
     </row>
     <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>458</v>
+        <v>236</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>28</v>
@@ -1973,7 +2043,7 @@
     </row>
     <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>459</v>
+        <v>237</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>29</v>
@@ -2017,7 +2087,7 @@
     </row>
     <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>460</v>
+        <v>238</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>30</v>
@@ -2061,7 +2131,7 @@
     </row>
     <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>461</v>
+        <v>239</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>31</v>
@@ -2105,7 +2175,7 @@
     </row>
     <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>462</v>
+        <v>240</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>32</v>
@@ -2149,7 +2219,7 @@
     </row>
     <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>463</v>
+        <v>241</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>33</v>
@@ -2193,7 +2263,7 @@
     </row>
     <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>464</v>
+        <v>242</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>34</v>
@@ -2237,7 +2307,7 @@
     </row>
     <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>465</v>
+        <v>243</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>35</v>
@@ -2281,7 +2351,7 @@
     </row>
     <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>466</v>
+        <v>244</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>36</v>
@@ -2325,7 +2395,7 @@
     </row>
     <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>467</v>
+        <v>245</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>37</v>
@@ -2369,7 +2439,7 @@
     </row>
     <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>468</v>
+        <v>246</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>38</v>
@@ -2413,7 +2483,7 @@
     </row>
     <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>469</v>
+        <v>247</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>39</v>
@@ -2457,7 +2527,7 @@
     </row>
     <row r="36" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>470</v>
+        <v>248</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>40</v>
@@ -2501,7 +2571,7 @@
     </row>
     <row r="37" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>471</v>
+        <v>249</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>41</v>
@@ -2545,7 +2615,7 @@
     </row>
     <row r="38" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>472</v>
+        <v>250</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>42</v>
@@ -2589,7 +2659,7 @@
     </row>
     <row r="39" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>473</v>
+        <v>251</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>43</v>
@@ -2633,7 +2703,7 @@
     </row>
     <row r="40" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>474</v>
+        <v>252</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>44</v>
@@ -2677,7 +2747,7 @@
     </row>
     <row r="41" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>475</v>
+        <v>253</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>45</v>
@@ -2721,7 +2791,7 @@
     </row>
     <row r="42" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>476</v>
+        <v>254</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>46</v>
@@ -2765,7 +2835,7 @@
     </row>
     <row r="43" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>477</v>
+        <v>255</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>47</v>
@@ -2809,7 +2879,7 @@
     </row>
     <row r="44" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>478</v>
+        <v>256</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>48</v>
@@ -2848,6 +2918,314 @@
         <v>0</v>
       </c>
       <c r="N44" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>257</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="8">
+        <v>0</v>
+      </c>
+      <c r="D45" s="8">
+        <v>0</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8">
+        <v>0</v>
+      </c>
+      <c r="H45" s="8">
+        <v>0</v>
+      </c>
+      <c r="I45" s="8">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8">
+        <v>0</v>
+      </c>
+      <c r="K45" s="8">
+        <v>0</v>
+      </c>
+      <c r="L45" s="8">
+        <v>0</v>
+      </c>
+      <c r="M45" s="8">
+        <v>0</v>
+      </c>
+      <c r="N45" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>258</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="9">
+        <v>0</v>
+      </c>
+      <c r="D46" s="9">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>0</v>
+      </c>
+      <c r="I46" s="9">
+        <v>0</v>
+      </c>
+      <c r="J46" s="9">
+        <v>0</v>
+      </c>
+      <c r="K46" s="9">
+        <v>0</v>
+      </c>
+      <c r="L46" s="9">
+        <v>0</v>
+      </c>
+      <c r="M46" s="9">
+        <v>0</v>
+      </c>
+      <c r="N46" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>259</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="8">
+        <v>0</v>
+      </c>
+      <c r="D47" s="8">
+        <v>0</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0</v>
+      </c>
+      <c r="F47" s="8">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8">
+        <v>0</v>
+      </c>
+      <c r="H47" s="8">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8">
+        <v>0</v>
+      </c>
+      <c r="K47" s="8">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8">
+        <v>0</v>
+      </c>
+      <c r="M47" s="8">
+        <v>0</v>
+      </c>
+      <c r="N47" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>260</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="9">
+        <v>0</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>0</v>
+      </c>
+      <c r="I48" s="9">
+        <v>0</v>
+      </c>
+      <c r="J48" s="9">
+        <v>0</v>
+      </c>
+      <c r="K48" s="9">
+        <v>0</v>
+      </c>
+      <c r="L48" s="9">
+        <v>0</v>
+      </c>
+      <c r="M48" s="9">
+        <v>0</v>
+      </c>
+      <c r="N48" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>261</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="8">
+        <v>0</v>
+      </c>
+      <c r="D49" s="8">
+        <v>0</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8">
+        <v>0</v>
+      </c>
+      <c r="M49" s="8">
+        <v>0</v>
+      </c>
+      <c r="N49" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>262</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="9">
+        <v>0</v>
+      </c>
+      <c r="D50" s="9">
+        <v>0</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>0</v>
+      </c>
+      <c r="I50" s="9">
+        <v>0</v>
+      </c>
+      <c r="J50" s="9">
+        <v>0</v>
+      </c>
+      <c r="K50" s="9">
+        <v>0</v>
+      </c>
+      <c r="L50" s="9">
+        <v>0</v>
+      </c>
+      <c r="M50" s="9">
+        <v>0</v>
+      </c>
+      <c r="N50" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>263</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="8">
+        <v>0</v>
+      </c>
+      <c r="D51" s="8">
+        <v>0</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0</v>
+      </c>
+      <c r="F51" s="8">
+        <v>0</v>
+      </c>
+      <c r="G51" s="8">
+        <v>0</v>
+      </c>
+      <c r="H51" s="8">
+        <v>0</v>
+      </c>
+      <c r="I51" s="8">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8">
+        <v>0</v>
+      </c>
+      <c r="K51" s="8">
+        <v>0</v>
+      </c>
+      <c r="L51" s="8">
+        <v>0</v>
+      </c>
+      <c r="M51" s="8">
+        <v>0</v>
+      </c>
+      <c r="N51" s="8">
         <v>0</v>
       </c>
     </row>
@@ -2875,7 +3253,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2885,12 +3263,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -2900,27 +3278,27 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -2930,12 +3308,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -2945,7 +3323,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/data/attendance/AMPHI_زهراوي_ادبي_1.xlsx
+++ b/data/attendance/AMPHI_زهراوي_ادبي_1.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:802cad91-388f-435c-8257-1d245c24bc4e</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:46a6adb3-93c6-412d-aaec-fc96a0919f31</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:3dcf69d8-4e8e-4743-8254-05fc98dda249</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d133b1c1-28a3-4b97-a9db-6b476ae244b4</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:68c9e7f1-d4ae-4293-b6b9-451268793a45</t>
         </r>
       </text>
@@ -93,13 +55,6 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:1b525255-15fd-4688-a952-6f984dd055a3</t>
         </r>
       </text>
@@ -107,13 +62,6 @@
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7e07fd69-a2ce-411a-bd6e-1c0f95d035f2</t>
         </r>
       </text>
@@ -121,13 +69,6 @@
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:04581ce8-2e3c-4c49-846b-d635898e21a5</t>
         </r>
       </text>
@@ -135,13 +76,6 @@
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:84ff47b8-ea13-44b3-ab36-236c6f8aab54</t>
         </r>
       </text>
@@ -149,13 +83,6 @@
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6a75f326-77ad-4d47-9e88-ead02d7c4b58</t>
         </r>
       </text>
@@ -163,13 +90,6 @@
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7978a3d1-f77e-4b38-af22-69725d451de5</t>
         </r>
       </text>
@@ -177,13 +97,6 @@
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6306692e-e7ab-4a1f-8f98-a70551e1751c</t>
         </r>
       </text>
@@ -191,13 +104,6 @@
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6d6c578a-c78b-438d-91c0-cf998c2750c3</t>
         </r>
       </text>
@@ -205,13 +111,6 @@
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:76c63291-be9c-482f-b4b0-1cabe917d476</t>
         </r>
       </text>
@@ -219,13 +118,6 @@
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7d1f60ce-c5d8-4377-91d6-6c4b6023e8f9</t>
         </r>
       </text>
@@ -233,13 +125,6 @@
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:17558c2a-1262-434a-97e3-56eca8a756b1</t>
         </r>
       </text>
@@ -247,13 +132,6 @@
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:706ecf15-8a21-4df2-9994-901d88ca9cdc</t>
         </r>
       </text>
@@ -261,13 +139,6 @@
     <comment ref="B22" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d5b643e6-acb1-4b43-b3b1-569248654a73</t>
         </r>
       </text>
@@ -275,13 +146,6 @@
     <comment ref="B23" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:e956e725-6d59-44da-adc3-a8bf8f10dbe4</t>
         </r>
       </text>
@@ -289,13 +153,6 @@
     <comment ref="B24" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:9a86b640-ceff-4413-93c3-8f7a5733ba8c</t>
         </r>
       </text>
@@ -303,13 +160,6 @@
     <comment ref="B25" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:0a7a2f76-33f3-4182-97bd-0e0dff2f6bac</t>
         </r>
       </text>
@@ -317,13 +167,6 @@
     <comment ref="B26" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b99e4fec-b8dd-4831-8de9-5233a20953d7</t>
         </r>
       </text>
@@ -331,13 +174,6 @@
     <comment ref="B27" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:f884f596-56ad-4371-b485-31a181e29eee</t>
         </r>
       </text>
@@ -345,13 +181,6 @@
     <comment ref="B28" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4919300a-6f37-4a88-9414-45316707a25f</t>
         </r>
       </text>
@@ -359,13 +188,6 @@
     <comment ref="B29" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:abbf565a-6277-46a7-9673-f053d01d6e24</t>
         </r>
       </text>
@@ -373,13 +195,6 @@
     <comment ref="B30" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:0a76d7d3-5f1e-4dc0-bb7d-59b454c144fc</t>
         </r>
       </text>
@@ -387,13 +202,6 @@
     <comment ref="B31" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:794959c2-b85f-46e1-a7e1-9c120b338d9a</t>
         </r>
       </text>
@@ -401,13 +209,6 @@
     <comment ref="B32" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:2225a3f3-9a6a-4517-8504-cf7b7da5d5f0</t>
         </r>
       </text>
@@ -415,13 +216,6 @@
     <comment ref="B33" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a2e18186-04fa-473c-9e6c-72d087462166</t>
         </r>
       </text>
@@ -429,13 +223,6 @@
     <comment ref="B34" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:84037c0c-016b-4072-a7bb-3edef521a833</t>
         </r>
       </text>
@@ -443,13 +230,6 @@
     <comment ref="B35" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6d9c17ac-0f55-4b43-bbb0-b4a1d10a404a</t>
         </r>
       </text>
@@ -457,13 +237,6 @@
     <comment ref="B36" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c2c5e8ca-a7bd-45e8-9793-c7720b5f46fc</t>
         </r>
       </text>
@@ -471,13 +244,6 @@
     <comment ref="B37" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:614f42a5-0e1f-46e7-88d6-c5f7783ee6ec</t>
         </r>
       </text>
@@ -485,13 +251,6 @@
     <comment ref="B38" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:cf2e9bc3-cc90-454c-8fbe-2a06de627a75</t>
         </r>
       </text>
@@ -499,13 +258,6 @@
     <comment ref="B39" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:f0305082-a3a6-46b2-b88c-e76058cb2fc4</t>
         </r>
       </text>
@@ -513,13 +265,6 @@
     <comment ref="B40" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:cd00920f-5475-4e56-90c2-daeadc54ef6d</t>
         </r>
       </text>
@@ -527,13 +272,6 @@
     <comment ref="B41" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:59b4f620-8e75-44c0-aadf-45cabeb9141e</t>
         </r>
       </text>
@@ -541,13 +279,6 @@
     <comment ref="B42" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:09d38764-9dd3-45fc-ab46-179050340c91</t>
         </r>
       </text>
@@ -555,13 +286,6 @@
     <comment ref="B43" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:940ee804-c513-440b-9492-b6f652d91570</t>
         </r>
       </text>
@@ -569,13 +293,6 @@
     <comment ref="B44" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:5688f6f9-82f1-418f-a5d0-191da4520e6e</t>
         </r>
       </text>
@@ -583,13 +300,6 @@
     <comment ref="B45" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:e19083e5-fb52-4474-9b87-f7ac097a6fde</t>
         </r>
       </text>
@@ -597,13 +307,6 @@
     <comment ref="B46" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7e4c10db-0e0f-4122-b9f3-003b7fbc4280</t>
         </r>
       </text>
@@ -611,13 +314,6 @@
     <comment ref="B47" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:1ef83844-49f4-4e07-9ba1-3a3d9c7f7fff</t>
         </r>
       </text>
@@ -625,13 +321,6 @@
     <comment ref="B48" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:dca6f60c-f366-4dfe-994a-e3534e9ea227</t>
         </r>
       </text>
@@ -639,13 +328,6 @@
     <comment ref="B49" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4915abfb-a955-4ab9-83c8-136c50fe6eae</t>
         </r>
       </text>
@@ -653,13 +335,6 @@
     <comment ref="B50" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:1b6a7a9c-c91b-4b10-9e37-4e4fac572776</t>
         </r>
       </text>
@@ -667,14 +342,42 @@
     <comment ref="B51" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:09fe61eb-a4f9-4ce6-b563-381fddcf72a0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0">
+      <text>
+        <r>
+          <t>student_id:94d34ea3-c206-4873-af58-455c6ec4c4e5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0">
+      <text>
+        <r>
+          <t>student_id:385bdebc-abbb-4e00-8b80-59d20f21e787</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0">
+      <text>
+        <r>
+          <t>student_id:ce6c1db1-5eae-42a1-8a75-bd75447f2f16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0">
+      <text>
+        <r>
+          <t>student_id:567bf27b-c434-42d4-a3c9-ceabbb1b7114</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0">
+      <text>
+        <r>
+          <t>student_id:9bccdfb6-5a9c-47bb-8da7-c64dedb3f5a9</t>
         </r>
       </text>
     </comment>
@@ -683,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="77">
   <si>
     <t>زهراوي ادبي 1  |  AMPHI  |  BAC  |  زهراوي</t>
   </si>
@@ -697,6 +400,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -715,6 +421,9 @@
     <t>26/09/2026</t>
   </si>
   <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -859,6 +568,21 @@
     <t>طيار عبد الرحيم</t>
   </si>
   <si>
+    <t>عيساني رتاج خديجة</t>
+  </si>
+  <si>
+    <t>قيطاني  يانيس</t>
+  </si>
+  <si>
+    <t>منتوري عبد الرحمان</t>
+  </si>
+  <si>
+    <t>شنوف شيماء</t>
+  </si>
+  <si>
+    <t>طبي افنان</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -886,7 +610,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -908,40 +635,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1028,7 +748,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1383,15 +1103,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N51"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N56"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1409,7 +1129,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1419,10 +1139,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -1464,54 +1187,54 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>217</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -1550,21 +1273,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>218</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
         <v>0</v>
@@ -1594,21 +1317,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>219</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="8">
         <v>0</v>
@@ -1638,21 +1361,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>220</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
@@ -1682,21 +1405,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>221</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -1726,21 +1449,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>222</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9">
         <v>0</v>
@@ -1770,21 +1493,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>223</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8">
         <v>0</v>
@@ -1814,21 +1537,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>224</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
@@ -1858,21 +1581,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>225</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="8">
         <v>0</v>
@@ -1902,21 +1625,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>226</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9">
         <v>0</v>
@@ -1946,21 +1669,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>227</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
@@ -1990,12 +1713,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>228</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" s="9">
         <v>0</v>
@@ -2004,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
@@ -2034,21 +1757,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>229</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="8">
         <v>0</v>
@@ -2078,21 +1801,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>230</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="9">
         <v>0</v>
@@ -2122,21 +1845,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>231</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C19" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="8">
         <v>0</v>
@@ -2166,21 +1889,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>232</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="9">
         <v>0</v>
@@ -2210,21 +1933,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>233</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="8">
         <v>0</v>
@@ -2254,21 +1977,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>234</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
@@ -2298,21 +2021,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>235</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="8">
         <v>0</v>
@@ -2342,21 +2065,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>236</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="9">
         <v>0</v>
@@ -2386,21 +2109,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>237</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="8">
         <v>0</v>
@@ -2430,21 +2153,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>238</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="9">
         <v>0</v>
@@ -2474,21 +2197,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>239</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="8">
         <v>0</v>
@@ -2518,21 +2241,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>240</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="9">
         <v>0</v>
@@ -2562,21 +2285,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>241</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="8">
         <v>0</v>
@@ -2606,21 +2329,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>242</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="9">
         <v>0</v>
@@ -2650,21 +2373,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>243</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="8">
         <v>0</v>
@@ -2694,21 +2417,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>244</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="9">
         <v>0</v>
       </c>
       <c r="E32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="9">
         <v>0</v>
@@ -2738,21 +2461,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>245</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="8">
         <v>0</v>
@@ -2782,21 +2505,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>246</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="9">
         <v>0</v>
@@ -2826,21 +2549,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>247</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="8">
         <v>0</v>
@@ -2870,21 +2593,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>248</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="9">
         <v>0</v>
@@ -2914,12 +2637,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>249</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C37" s="8">
         <v>0</v>
@@ -2928,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="8">
         <v>0</v>
@@ -2958,21 +2681,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>250</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="9">
         <v>0</v>
@@ -3002,21 +2725,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>251</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="8">
         <v>0</v>
@@ -3046,21 +2769,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>252</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="9">
         <v>0</v>
@@ -3090,21 +2813,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>253</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C41" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="8">
         <v>0</v>
@@ -3134,21 +2857,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>254</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C42" s="9">
         <v>0</v>
       </c>
       <c r="D42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="9">
         <v>0</v>
@@ -3178,21 +2901,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>255</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C43" s="8">
         <v>0</v>
       </c>
       <c r="D43" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="8">
         <v>0</v>
@@ -3222,21 +2945,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>256</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C44" s="9">
         <v>0</v>
       </c>
       <c r="D44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="9">
         <v>0</v>
@@ -3266,21 +2989,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>257</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C45" s="8">
         <v>0</v>
       </c>
       <c r="D45" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="8">
         <v>0</v>
@@ -3310,21 +3033,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>258</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C46" s="9">
         <v>0</v>
       </c>
       <c r="D46" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="9">
         <v>0</v>
@@ -3354,12 +3077,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>259</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C47" s="8">
         <v>0</v>
@@ -3368,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="8">
         <v>0</v>
@@ -3398,12 +3121,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>260</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C48" s="9">
         <v>0</v>
@@ -3412,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="9">
         <v>0</v>
@@ -3442,12 +3165,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>261</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C49" s="8">
         <v>0</v>
@@ -3456,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="8">
         <v>0</v>
@@ -3486,12 +3209,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>262</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C50" s="9">
         <v>0</v>
@@ -3500,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="9">
         <v>0</v>
@@ -3530,12 +3253,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>263</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C51" s="8">
         <v>0</v>
@@ -3544,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="8">
         <v>0</v>
@@ -3571,6 +3294,226 @@
         <v>0</v>
       </c>
       <c r="N51" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>292</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" s="9">
+        <v>0</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>0</v>
+      </c>
+      <c r="I52" s="9">
+        <v>0</v>
+      </c>
+      <c r="J52" s="9">
+        <v>0</v>
+      </c>
+      <c r="K52" s="9">
+        <v>0</v>
+      </c>
+      <c r="L52" s="9">
+        <v>0</v>
+      </c>
+      <c r="M52" s="9">
+        <v>0</v>
+      </c>
+      <c r="N52" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>335</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="8">
+        <v>0</v>
+      </c>
+      <c r="D53" s="8">
+        <v>0</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+      <c r="K53" s="8">
+        <v>0</v>
+      </c>
+      <c r="L53" s="8">
+        <v>0</v>
+      </c>
+      <c r="M53" s="8">
+        <v>0</v>
+      </c>
+      <c r="N53" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>828</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="9">
+        <v>0</v>
+      </c>
+      <c r="D54" s="9">
+        <v>0</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>0</v>
+      </c>
+      <c r="I54" s="9">
+        <v>0</v>
+      </c>
+      <c r="J54" s="9">
+        <v>0</v>
+      </c>
+      <c r="K54" s="9">
+        <v>0</v>
+      </c>
+      <c r="L54" s="9">
+        <v>0</v>
+      </c>
+      <c r="M54" s="9">
+        <v>0</v>
+      </c>
+      <c r="N54" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>911</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0</v>
+      </c>
+      <c r="D55" s="8">
+        <v>0</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8">
+        <v>0</v>
+      </c>
+      <c r="M55" s="8">
+        <v>0</v>
+      </c>
+      <c r="N55" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>912</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="9">
+        <v>0</v>
+      </c>
+      <c r="D56" s="9">
+        <v>0</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0</v>
+      </c>
+      <c r="F56" s="9">
+        <v>0</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9">
+        <v>0</v>
+      </c>
+      <c r="I56" s="9">
+        <v>0</v>
+      </c>
+      <c r="J56" s="9">
+        <v>0</v>
+      </c>
+      <c r="K56" s="9">
+        <v>0</v>
+      </c>
+      <c r="L56" s="9">
+        <v>0</v>
+      </c>
+      <c r="M56" s="9">
+        <v>0</v>
+      </c>
+      <c r="N56" s="9">
         <v>0</v>
       </c>
     </row>
@@ -3580,7 +3523,7 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -3590,89 +3533,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>